--- a/docs/검토요청사항_회신_261018.xlsx
+++ b/docs/검토요청사항_회신_261018.xlsx
@@ -600,13 +600,13 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>① 압정 6칸을 채우고 조사개황 오른쪽 위 [새 지점]
-② 6칸은 남고 지점·종 입력은 비었는지 본다</t>
+          <t>① 6칸을 채우고 조사개황 오른쪽 위 [새 지점]
+② 압정을 끈 칸까지 6칸이 남고 지점·종 입력은 비었는지 본다</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>[새 지점]은 압정을 꺼 둔 칸도 6칸 모두 남깁니다.</t>
+          <t>[새 지점]은 압정과 관계없이 6칸을 모두 남깁니다. 압정은 앱을 다시 켤 때 그 값을 채우는 기능입니다.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>반영 — 조사개황 오른쪽 위에 [새 지점] 버튼을 넣었습니다. 압정 6칸(대분류·연도차수·조사일자·날씨·조사자·조사기관)은 남기고 지점·하천명·사업장·좌표·권역·하천유형과 7개 분류군 입력을 비운 뒤 지점명 칸으로 갑니다.</t>
+          <t>반영 — 조사개황 오른쪽 위에 [새 지점] 버튼을 넣었습니다. 대분류·연도차수·조사일자·날씨·조사자·조사기관 6칸은 압정과 관계없이 남기고 지점·하천명·사업장·좌표·권역·하천유형과 7개 분류군 입력을 비운 뒤 지점명 칸으로 갑니다.</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>반영 — 지점을 고르면 대권역·중권역이 하천 단위로 자동으로 채워집니다(곡교천 권역 → 금강/삽교천, 오산천·원천리천 → 한강/안성천). 채운 뒤 고칠 수 있습니다.</t>
+          <t>반영 — 곡교천·오산천·원천리천 하천의 지점을 고르면 대권역·중권역이 하천 단위로 자동으로 채워집니다(곡교천 권역 → 금강/삽교천, 오산천·원천리천 → 한강/안성천). 채운 뒤 고칠 수 있습니다.</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>참고: 2026-03 제출 자료에 곡교천 권역 20건이 한강/안성천으로 잘못 들어가 있었습니다(손으로 적은 결과). 생태현황 지점 중 위 세 하천이 아닌 곳(진위천 등)은 비어 있으니 목록에서 고르거나 직접 적습니다.</t>
+          <t>참고: 2026-03 제출 자료에 곡교천 권역 20건이 한강/안성천으로 잘못 들어가 있었습니다(손으로 적은 결과). 생태현황 지점 중 그 밖의 하천(진위천·안성천 등)은 비어 있으니 목록에서 고르거나 직접 적습니다.</t>
         </is>
       </c>
     </row>

--- a/docs/검토요청사항_회신_261018.xlsx
+++ b/docs/검토요청사항_회신_261018.xlsx
@@ -1153,17 +1153,19 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>반영 안 함(사유: 개체밀도로 바꾸는 환산식과 조사도구별 면적 규약이 양식·관리자 계산에 정해져 있지 않습니다) — 총 개체수는 지금처럼 실측 개체수입니다.</t>
+          <t>반영 — 실측 개체수는 그대로 두고, 화면 건강성과 보고서 엑셀에 개체밀도(inds./㎡)를 함께 표시합니다. 채집 면적은 Surber 30×30 0.09㎡ · 50×50 0.25㎡ · 에크만 0.0225㎡ × 조사 횟수로 계산합니다.</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>① 저서동물 건강성 → 총 개체수가 입력한 개체수의 합인지 본다</t>
+          <t>① 저서동물 조사환경에 Surber 30×30 3회를 넣는다
+② 건강성의 개체밀도가 '총 개체수 ÷ 0.27'인지 본다
+③ [보고서 엑셀]에서 출현종 표의 개체밀도 열을 확인한다</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>환산식과 도구별 면적(Surber 30×30 · 50×50 · 드렛지 · 에크만)을 정해 주시면 반영을 검토하겠습니다. 채집기별 조사 횟수는 지금도 입력·저장됩니다.</t>
+          <t>드렛지/D-Net 은 면적 기준이 없어 환산하지 않습니다(끄는 거리·폭 기준을 주시면 반영하겠습니다). 에크만 크기가 15×15cm 와 다르면 알려 주십시오. 건강성 등급(BMI) 등 지수는 실측 개체수 기준이며 환산과 관계없이 같습니다.</t>
         </is>
       </c>
     </row>
